--- a/inst/extdata/codelist.xlsx
+++ b/inst/extdata/codelist.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\NA\MAF\MAF_Privat\Miljogifter\mg_analys\SGU\MoCiS2_temp\MoCiS2\inst\extdata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\annesore\github\MoCiS2\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AB86AA4-C9D0-4864-941D-8F50854E7060}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{524D8DB3-AF48-4CA1-B9C2-E8D3572652F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="300" yWindow="120" windowWidth="27435" windowHeight="16635" tabRatio="877" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2250" yWindow="450" windowWidth="19950" windowHeight="20115" tabRatio="877" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="STATIONER" sheetId="14" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1755" uniqueCount="732">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1755" uniqueCount="729">
   <si>
     <t>PERC</t>
   </si>
@@ -372,15 +372,6 @@
   </si>
   <si>
     <t>Ängskärsklubb</t>
-  </si>
-  <si>
-    <t>BYXE</t>
-  </si>
-  <si>
-    <t>00103946</t>
-  </si>
-  <si>
-    <t>Byxelkrok</t>
   </si>
   <si>
     <t>FLAD</t>
@@ -2738,13 +2729,13 @@
         <v>97</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -2755,10 +2746,10 @@
         <v>99</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -2769,10 +2760,10 @@
         <v>99</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -2783,10 +2774,10 @@
         <v>99</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="D4" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -2797,10 +2788,10 @@
         <v>101</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -2811,10 +2802,10 @@
         <v>101</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -2825,10 +2816,10 @@
         <v>101</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="D7" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -2839,10 +2830,10 @@
         <v>103</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -2853,10 +2844,10 @@
         <v>103</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -2867,10 +2858,10 @@
         <v>103</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="D10" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -2881,10 +2872,10 @@
         <v>105</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -2895,10 +2886,10 @@
         <v>105</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -2909,10 +2900,10 @@
         <v>105</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="D13" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -2940,236 +2931,236 @@
         <v>111</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>112</v>
+        <v>314</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D21" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B32" s="16" t="s">
         <v>110</v>
@@ -3178,889 +3169,889 @@
         <v>111</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B35" s="16" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B36" s="16" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B37" s="16" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B39" s="16" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D39" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B40" s="16" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B41" s="16" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B42" s="16" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B43" s="16" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B44" s="16" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B45" s="16" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B46" s="18" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B47" s="16" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="9" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="9" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="9" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="9" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="9" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="9" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="9" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="9" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="9" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="9" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="9" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="9" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="9" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="9" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="9" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="D62" s="9" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="9" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="9" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="D64" s="9" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="9" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="9" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="C66" s="9" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="9" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="B67" s="10" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="C67" s="9" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="D67" s="9" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="11" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="B68" s="10" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="9" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="B69" s="10" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="C69" s="9" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="D69" s="9" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="9" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="B70" s="10" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="9" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B71" s="10" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C71" s="9" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="D71" s="9" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="9" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="B72" s="10" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C72" s="9" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="D72" s="9" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="11" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="B73" s="10" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="D73" s="11" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="9" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="B74" s="10" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="C74" s="9" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="D74" s="9" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="9" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="B75" s="10" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="C75" s="9" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D75" s="9" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="9" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="B76" s="10" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="C76" s="9" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="D76" s="9" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="9" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="B77" s="10" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="9" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="B78" s="10" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="C78" s="9" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="D78" s="9" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="9" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="B79" s="10" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="C79" s="9" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="D79" s="9" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="9" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="B80" s="10" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="C80" s="9" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="D80" s="9" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="9" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="B81" s="16" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="C81" s="9" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="D81" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="9" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="B82" s="16" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="C82" s="9" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="D82" s="9" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="9" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="B83" s="16" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="C83" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="D83" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="9" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="B84" s="16" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="C84" s="9" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="D84" s="9" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B85" s="16" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D85" s="7" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="21" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="B86" s="16" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="C86" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="D86" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="21" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="B87" s="16" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="C87" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="D87" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" s="21" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="B88" s="16" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="C88" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="D88" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="21" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="B89" s="16" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="C89" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="D89" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="21" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="B90" s="16" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="C90" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="D90" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="21" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="B91" s="16" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="C91" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="D91" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="21" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="B92" s="16" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="C92" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="D92" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" s="21" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="B93" s="16" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="C93" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="D93" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="21" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="B94" s="16" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="C94" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="D94" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="21" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="B95" s="16" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="C95" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="D95" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
     </row>
   </sheetData>
@@ -4085,10 +4076,10 @@
         <v>96</v>
       </c>
       <c r="C1" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="D1" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -4102,7 +4093,7 @@
         <v>206198</v>
       </c>
       <c r="D2" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -4116,7 +4107,7 @@
         <v>106665</v>
       </c>
       <c r="D3" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -4130,12 +4121,12 @@
         <v>102618</v>
       </c>
       <c r="D4" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="B5" t="s">
         <v>6</v>
@@ -4144,12 +4135,12 @@
         <v>206139</v>
       </c>
       <c r="D5" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="B6" t="s">
         <v>7</v>
@@ -4158,7 +4149,7 @@
         <v>206231</v>
       </c>
       <c r="D6" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -4172,7 +4163,7 @@
         <v>100144</v>
       </c>
       <c r="D7" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -4186,7 +4177,7 @@
         <v>102950</v>
       </c>
       <c r="D8" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -4194,13 +4185,13 @@
         <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="C9">
         <v>206293</v>
       </c>
       <c r="D9" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -4214,7 +4205,7 @@
         <v>206142</v>
       </c>
       <c r="D10" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -4222,69 +4213,69 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="C11">
         <v>206089</v>
       </c>
       <c r="D11" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="B12" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="C12">
         <v>206135</v>
       </c>
       <c r="D12" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="B13" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="C13">
         <v>102708</v>
       </c>
       <c r="D13" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="B14" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C14" s="20">
         <v>100068</v>
       </c>
       <c r="D14" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="B15" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="C15">
         <v>100104</v>
       </c>
       <c r="D15" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
     </row>
   </sheetData>
@@ -4322,7 +4313,7 @@
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="B1" t="s">
         <v>16</v>
@@ -4331,51 +4322,51 @@
         <v>17</v>
       </c>
       <c r="D1" t="s">
+        <v>332</v>
+      </c>
+      <c r="E1" t="s">
+        <v>344</v>
+      </c>
+      <c r="F1" t="s">
+        <v>331</v>
+      </c>
+      <c r="G1" t="s">
+        <v>333</v>
+      </c>
+      <c r="H1" t="s">
+        <v>499</v>
+      </c>
+      <c r="I1" t="s">
+        <v>498</v>
+      </c>
+      <c r="J1" t="s">
+        <v>334</v>
+      </c>
+      <c r="K1" t="s">
         <v>335</v>
       </c>
-      <c r="E1" t="s">
-        <v>347</v>
-      </c>
-      <c r="F1" t="s">
-        <v>334</v>
-      </c>
-      <c r="G1" t="s">
-        <v>336</v>
-      </c>
-      <c r="H1" t="s">
-        <v>502</v>
-      </c>
-      <c r="I1" t="s">
-        <v>501</v>
-      </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>337</v>
       </c>
-      <c r="K1" t="s">
-        <v>338</v>
-      </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
+        <v>339</v>
+      </c>
+      <c r="N1" t="s">
         <v>340</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
+        <v>341</v>
+      </c>
+      <c r="P1" t="s">
         <v>342</v>
       </c>
-      <c r="N1" t="s">
+      <c r="Q1" t="s">
         <v>343</v>
-      </c>
-      <c r="O1" t="s">
-        <v>344</v>
-      </c>
-      <c r="P1" t="s">
-        <v>345</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
@@ -4384,22 +4375,22 @@
         <v>19</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="L2" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
@@ -4407,28 +4398,28 @@
         <v>20</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="C3" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
@@ -4442,22 +4433,22 @@
         <v>23</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
@@ -4471,22 +4462,22 @@
         <v>26</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
@@ -4497,25 +4488,25 @@
         <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
@@ -4529,22 +4520,22 @@
         <v>31</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
@@ -4558,22 +4549,22 @@
         <v>34</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
@@ -4587,27 +4578,27 @@
         <v>37</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="B10" t="s">
         <v>49</v>
@@ -4616,22 +4607,22 @@
         <v>50</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
@@ -4645,22 +4636,22 @@
         <v>50</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
@@ -4674,27 +4665,27 @@
         <v>52</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B13" t="s">
         <v>53</v>
@@ -4703,22 +4694,22 @@
         <v>54</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
@@ -4732,56 +4723,56 @@
         <v>56</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="B15" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="B16" t="s">
         <v>57</v>
@@ -4790,22 +4781,22 @@
         <v>58</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="L16" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
@@ -4819,27 +4810,27 @@
         <v>58</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="L17" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="B18" t="s">
         <v>59</v>
@@ -4848,22 +4839,22 @@
         <v>60</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="L18" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
@@ -4877,27 +4868,27 @@
         <v>60</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="L19" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="B20" t="s">
         <v>61</v>
@@ -4906,22 +4897,22 @@
         <v>62</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="K20" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="L20" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
@@ -4935,27 +4926,27 @@
         <v>62</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="L21" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="B22" t="s">
         <v>63</v>
@@ -4964,22 +4955,22 @@
         <v>64</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="L22" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
@@ -4993,27 +4984,27 @@
         <v>64</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="K23" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="L23" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="B24" t="s">
         <v>65</v>
@@ -5022,22 +5013,22 @@
         <v>66</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="K24" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="L24" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
@@ -5051,51 +5042,51 @@
         <v>66</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="K25" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="L25" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="B26" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="C26" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="I26" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="K26" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="L26" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
@@ -5109,22 +5100,22 @@
         <v>68</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="I27" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="K27" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="L27" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
@@ -5138,27 +5129,27 @@
         <v>70</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="I28" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="J28" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="K28" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="L28" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="B29" t="s">
         <v>71</v>
@@ -5167,22 +5158,22 @@
         <v>72</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="K29" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="L29" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
@@ -5196,80 +5187,80 @@
         <v>72</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="I30" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="J30" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="K30" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="L30" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="B31" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="C31" t="s">
         <v>73</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="I31" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="J31" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="K31" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="L31" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="B32" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="C32" t="s">
         <v>74</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H32" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="I32" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="J32" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="K32" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="L32" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
@@ -5277,28 +5268,28 @@
         <v>75</v>
       </c>
       <c r="B33" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="C33" t="s">
         <v>76</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="I33" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="K33" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="L33" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
@@ -5306,28 +5297,28 @@
         <v>77</v>
       </c>
       <c r="B34" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="C34" t="s">
         <v>78</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="K34" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="L34" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
@@ -5335,1684 +5326,1684 @@
         <v>79</v>
       </c>
       <c r="B35" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="C35" t="s">
         <v>80</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="I35" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="K35" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="L35" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="B36" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="C36" t="s">
         <v>81</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H36" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="I36" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="J36" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="K36" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="L36" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="B37" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="C37" t="s">
         <v>82</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="I37" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="J37" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="K37" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="L37" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="B38" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="C38" t="s">
         <v>83</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H38" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="I38" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="J38" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="K38" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="L38" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="B39" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="C39" t="s">
         <v>84</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="I39" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="J39" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="K39" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="L39" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="B40" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="C40" t="s">
         <v>85</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H40" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="I40" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="J40" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="K40" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="L40" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="B41" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="C41" t="s">
         <v>86</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H41" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="I41" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="J41" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="K41" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="L41" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="B42" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="C42" t="s">
         <v>87</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H42" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="I42" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="J42" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="K42" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="L42" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="B43" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="C43" t="s">
         <v>88</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H43" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="I43" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="J43" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="K43" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="L43" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="B44" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="C44" t="s">
         <v>89</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H44" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="I44" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="J44" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="K44" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="L44" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="B45" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="C45" t="s">
         <v>90</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="I45" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="J45" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="K45" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="L45" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="B46" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="C46" t="s">
         <v>91</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H46" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="I46" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="J46" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="K46" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="L46" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="B47" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="C47" t="s">
         <v>92</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="I47" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="J47" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="K47" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="L47" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="B48" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="C48" t="s">
         <v>93</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H48" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="I48" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="J48" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="K48" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="L48" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="B49" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="C49" t="s">
         <v>94</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H49" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="I49" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="J49" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="K49" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="L49" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="B50" s="24" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="C50" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H50" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="I50" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="J50" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="K50" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="L50" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="B51" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="C51" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H51" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="I51" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="J51" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="K51" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="L51" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="B52" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="C52" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H52" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="I52" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="J52" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="K52" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="L52" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="B53" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="C53" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H53" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="I53" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="J53" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="K53" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="L53" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="B54" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="C54" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="G54" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H54" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="I54" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="J54" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="K54" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="L54" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="B55" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="C55" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H55" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="I55" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="J55" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="K55" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="L55" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="B56" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="C56" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="G56" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H56" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="I56" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="J56" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="K56" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="L56" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="B57" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="C57" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="G57" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H57" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="I57" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="J57" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="K57" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="L57" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="B58" s="23" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="C58" s="23" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="G58" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H58" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="I58" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="J58" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="K58" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="L58" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="B59" s="23" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="C59" s="23" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="G59" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H59" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="I59" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="J59" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="K59" s="7" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="L59" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B60" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="C60" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="G60" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H60" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="I60" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="J60" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="K60" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="L60" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B61" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="C61" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="G61" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H61" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="I61" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="J61" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="K61" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="L61" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B62" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="C62" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G62" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H62" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="I62" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="J62" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="K62" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="L62" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B63" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="C63" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="G63" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H63" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="I63" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="J63" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="K63" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="L63" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B64" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="C64" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G64" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H64" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="I64" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="J64" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="K64" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="L64" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B65" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="C65" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="G65" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H65" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="I65" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="J65" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="K65" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="L65" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B66" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="C66" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="G66" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H66" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="I66" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="J66" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="K66" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="L66" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B67" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="C67" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="G67" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H67" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="I67" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="J67" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="K67" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="L67" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B68" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="C68" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="G68" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H68" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="I68" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="J68" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="K68" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="L68" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="B69" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="C69" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G69" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H69" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="I69" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="J69" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="K69" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="L69" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B70" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="C70" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="G70" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H70" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="I70" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="J70" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="K70" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="L70" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B71" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="C71" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="G71" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H71" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="I71" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="J71" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="K71" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="L71" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B72" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="C72" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="G72" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H72" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="I72" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="J72" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="K72" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="L72" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B73" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="C73" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="G73" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H73" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="I73" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="J73" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="K73" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="L73" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B74" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="C74" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="G74" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H74" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="I74" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="J74" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="K74" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="L74" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B75" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="C75" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="G75" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H75" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="I75" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="J75" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="K75" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="L75" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B76" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="C76" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="G76" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H76" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="I76" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="J76" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="K76" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="L76" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="B77" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="G77" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="H77" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="I77" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="J77" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="K77" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="L77" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B78" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="G78" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="H78" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="I78" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="J78" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="K78" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="L78" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B79" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="G79" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="H79" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="I79" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="J79" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="K79" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="L79" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B80" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="G80" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="H80" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="I80" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="J80" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="K80" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="L80" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B81" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="G81" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="H81" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="I81" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="J81" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="K81" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="L81" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" s="5" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="B82" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="G82" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="H82" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="I82" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="J82" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="K82" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="L82" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" s="5" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B83" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="G83" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="H83" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="I83" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="J83" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="K83" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="L83" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" s="5" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B84" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="G84" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="H84" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="I84" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="J84" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="K84" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="L84" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" s="5" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="B85" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="G85" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="H85" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="I85" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="J85" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="K85" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="L85" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" s="5" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="B86" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="G86" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="H86" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="I86" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="J86" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="K86" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="L86" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" s="5" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="B87" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="G87" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="H87" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="I87" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="J87" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="K87" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="L87" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" s="5" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="B88" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="G88" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="H88" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="I88" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="J88" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="K88" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="L88" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" s="5" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="B89" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="G89" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="H89" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="I89" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="J89" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="K89" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="L89" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" s="5" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B90" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="G90" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="H90" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="I90" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="J90" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="K90" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="L90" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91" s="5" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B91" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="G91" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="H91" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="I91" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="J91" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="K91" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="L91" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92" s="14" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="B92" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="D92" s="7"/>
       <c r="E92" s="7"/>
       <c r="F92" s="8"/>
       <c r="G92" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="H92" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="I92" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="J92" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="K92" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="L92" s="7" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="M92" s="7"/>
       <c r="N92" s="7"/>
@@ -7022,34 +7013,34 @@
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93" s="14" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B93" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="D93" s="7"/>
       <c r="E93" s="7"/>
       <c r="F93" s="8"/>
       <c r="G93" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="H93" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="I93" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="J93" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="K93" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="L93" s="7" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="M93" s="7"/>
       <c r="N93" s="7"/>
@@ -7059,34 +7050,34 @@
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94" s="14" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="B94" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="D94" s="7"/>
       <c r="E94" s="7"/>
       <c r="F94" s="8"/>
       <c r="G94" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="H94" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="I94" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="J94" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="K94" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="L94" s="7" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="M94" s="7"/>
       <c r="N94" s="7"/>
@@ -7096,34 +7087,34 @@
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95" s="15" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="B95" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="D95" s="7"/>
       <c r="E95" s="7"/>
       <c r="F95" s="8"/>
       <c r="G95" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="H95" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="I95" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="J95" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="K95" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="L95" s="7" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="M95" s="7"/>
       <c r="N95" s="7"/>
@@ -7133,34 +7124,34 @@
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96" s="15" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B96" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="D96" s="7"/>
       <c r="E96" s="7"/>
       <c r="F96" s="8"/>
       <c r="G96" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="H96" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="I96" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="J96" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="K96" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="L96" s="7" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="M96" s="7"/>
       <c r="N96" s="7"/>
@@ -7170,34 +7161,34 @@
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97" s="15" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="B97" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="D97" s="7"/>
       <c r="E97" s="7"/>
       <c r="F97" s="8"/>
       <c r="G97" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="H97" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="I97" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="J97" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="K97" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="L97" s="7" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="M97" s="7"/>
       <c r="N97" s="7"/>
@@ -7207,34 +7198,34 @@
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98" s="15" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="B98" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="D98" s="7"/>
       <c r="E98" s="7"/>
       <c r="F98" s="8"/>
       <c r="G98" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="H98" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="I98" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="J98" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="K98" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="L98" s="7" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="M98" s="7"/>
       <c r="N98" s="7"/>
@@ -7244,34 +7235,34 @@
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99" s="15" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="B99" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="D99" s="7"/>
       <c r="E99" s="7"/>
       <c r="F99" s="8"/>
       <c r="G99" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="H99" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="I99" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="J99" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="K99" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="L99" s="7" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="M99" s="7"/>
       <c r="N99" s="7"/>
@@ -7281,34 +7272,34 @@
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100" s="15" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="B100" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="D100" s="7"/>
       <c r="E100" s="7"/>
       <c r="F100" s="8"/>
       <c r="G100" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="H100" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="I100" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="J100" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="K100" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="L100" s="7" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="M100" s="7"/>
       <c r="N100" s="7"/>
@@ -7318,34 +7309,34 @@
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101" s="15" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="B101" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="C101" s="7" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D101" s="7"/>
       <c r="E101" s="7"/>
       <c r="F101" s="8"/>
       <c r="G101" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="H101" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="I101" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="J101" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="K101" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="L101" s="7" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="M101" s="7"/>
       <c r="N101" s="7"/>
@@ -7355,34 +7346,34 @@
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A102" s="14" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B102" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="C102" s="7" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="D102" s="7"/>
       <c r="E102" s="7"/>
       <c r="F102" s="8"/>
       <c r="G102" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="H102" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="I102" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="J102" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="K102" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="L102" s="7" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="M102" s="7"/>
       <c r="N102" s="7"/>
@@ -7392,34 +7383,34 @@
     </row>
     <row r="103" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103" s="14" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="B103" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="D103" s="7"/>
       <c r="E103" s="7"/>
       <c r="F103" s="8"/>
       <c r="G103" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="H103" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="I103" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="J103" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="K103" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="L103" s="7" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="M103" s="7"/>
       <c r="N103" s="7"/>
@@ -7429,34 +7420,34 @@
     </row>
     <row r="104" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104" s="14" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="B104" s="22" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="D104" s="7"/>
       <c r="E104" s="7"/>
       <c r="F104" s="8"/>
       <c r="G104" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="H104" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="I104" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="J104" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="K104" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="L104" s="7" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="M104" s="7"/>
       <c r="N104" s="7"/>
@@ -7466,34 +7457,34 @@
     </row>
     <row r="105" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A105" s="15" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="B105" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="C105" s="7" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="D105" s="7"/>
       <c r="E105" s="7"/>
       <c r="F105" s="8"/>
       <c r="G105" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="H105" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="I105" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="J105" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="K105" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="L105" s="7" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="M105" s="7"/>
       <c r="N105" s="7"/>
@@ -7503,518 +7494,518 @@
     </row>
     <row r="106" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A106" s="12" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B106" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="C106" s="7" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="G106" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H106" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="I106" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="J106" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="K106" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="L106" s="7" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
     </row>
     <row r="107" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A107" s="12" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B107" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="C107" s="7" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="G107" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H107" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="I107" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="J107" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="K107" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="L107" s="7" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
     </row>
     <row r="108" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A108" s="12" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B108" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="C108" s="7" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="G108" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H108" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="I108" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="J108" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="K108" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="L108" s="7" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
     </row>
     <row r="109" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A109" s="12" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B109" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="C109" s="7" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="G109" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H109" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="I109" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="J109" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="K109" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="L109" s="7" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
     </row>
     <row r="110" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A110" s="12" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B110" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="C110" s="16" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="G110" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H110" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="I110" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="J110" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="K110" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="L110" s="7" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
     </row>
     <row r="111" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A111" s="12" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B111" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="C111" s="7" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="G111" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H111" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="I111" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="J111" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="K111" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="L111" s="7" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
     </row>
     <row r="112" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A112" s="12" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B112" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="C112" s="7" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="G112" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H112" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="I112" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="J112" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="K112" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="L112" s="7" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
     </row>
     <row r="113" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A113" s="12" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B113" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="C113" s="7" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="G113" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H113" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="I113" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="J113" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="K113" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="L113" s="7" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
     </row>
     <row r="114" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A114" s="12" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B114" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="C114" s="7" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="G114" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H114" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="I114" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="J114" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="K114" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="L114" s="7" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
     </row>
     <row r="115" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A115" s="12" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B115" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="C115" s="7" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="G115" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H115" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="I115" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="J115" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="K115" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="L115" s="7" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
     </row>
     <row r="116" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A116" s="12" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B116" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="C116" s="7" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="G116" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H116" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="I116" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="J116" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="K116" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="L116" s="7" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
     </row>
     <row r="117" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A117" s="12" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="B117" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="C117" s="7" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G117" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H117" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="I117" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="J117" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="K117" s="7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="L117" s="7" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
     </row>
     <row r="118" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A118" s="5" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="B118" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C118" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="E118" s="13" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="G118" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="J118" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="K118" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="L118" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
     </row>
     <row r="119" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A119" s="5" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="B119" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C119" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="E119" s="13" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="G119" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="J119" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="K119" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="L119" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
     </row>
     <row r="120" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A120" s="5" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="B120" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C120" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D120" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="E120" s="13" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="G120" s="13" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="J120" s="13" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="K120" s="17"/>
       <c r="L120" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="M120" t="s">
+        <v>629</v>
+      </c>
+      <c r="N120" t="s">
+        <v>630</v>
+      </c>
+      <c r="O120" t="s">
+        <v>631</v>
+      </c>
+      <c r="P120" t="s">
+        <v>628</v>
+      </c>
+      <c r="Q120" t="s">
         <v>632</v>
-      </c>
-      <c r="N120" t="s">
-        <v>633</v>
-      </c>
-      <c r="O120" t="s">
-        <v>634</v>
-      </c>
-      <c r="P120" t="s">
-        <v>631</v>
-      </c>
-      <c r="Q120" t="s">
-        <v>635</v>
       </c>
     </row>
     <row r="121" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A121" s="5" t="s">
+        <v>538</v>
+      </c>
+      <c r="B121" t="s">
+        <v>301</v>
+      </c>
+      <c r="C121" t="s">
+        <v>302</v>
+      </c>
+      <c r="D121" t="s">
+        <v>638</v>
+      </c>
+      <c r="E121" s="13" t="s">
         <v>541</v>
       </c>
-      <c r="B121" t="s">
-        <v>304</v>
-      </c>
-      <c r="C121" t="s">
-        <v>305</v>
-      </c>
-      <c r="D121" t="s">
-        <v>641</v>
-      </c>
-      <c r="E121" s="13" t="s">
-        <v>544</v>
-      </c>
       <c r="G121" s="13" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="J121" s="13" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="K121" s="17"/>
       <c r="L121" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="M121" t="s">
+        <v>629</v>
+      </c>
+      <c r="N121" t="s">
+        <v>630</v>
+      </c>
+      <c r="O121" t="s">
+        <v>631</v>
+      </c>
+      <c r="P121" t="s">
+        <v>628</v>
+      </c>
+      <c r="Q121" t="s">
         <v>632</v>
-      </c>
-      <c r="N121" t="s">
-        <v>633</v>
-      </c>
-      <c r="O121" t="s">
-        <v>634</v>
-      </c>
-      <c r="P121" t="s">
-        <v>631</v>
-      </c>
-      <c r="Q121" t="s">
-        <v>635</v>
       </c>
     </row>
     <row r="122" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A122" s="5" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="B122" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="C122" s="7" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="D122" s="7"/>
       <c r="E122" s="7"/>
       <c r="F122" s="7"/>
       <c r="G122" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="H122" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="I122" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="J122" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="K122" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="L122" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="M122" s="7"/>
       <c r="N122" s="7"/>
@@ -8024,34 +8015,34 @@
     </row>
     <row r="123" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A123" s="5" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="B123" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="C123" s="7" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="D123" s="7"/>
       <c r="E123" s="7"/>
       <c r="F123" s="7"/>
       <c r="G123" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="H123" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="I123" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="J123" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="K123" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="L123" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="M123" s="7"/>
       <c r="N123" s="7"/>
@@ -8061,34 +8052,34 @@
     </row>
     <row r="124" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A124" s="5" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="B124" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="C124" s="7" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="D124" s="7"/>
       <c r="E124" s="7"/>
       <c r="F124" s="7"/>
       <c r="G124" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="H124" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="I124" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="J124" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="K124" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="L124" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="M124" s="7"/>
       <c r="N124" s="7"/>
@@ -8098,34 +8089,34 @@
     </row>
     <row r="125" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A125" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="B125" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="C125" s="7" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="D125" s="7"/>
       <c r="E125" s="7"/>
       <c r="F125" s="7"/>
       <c r="G125" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="H125" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="I125" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="J125" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="K125" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="L125" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="M125" s="7"/>
       <c r="N125" s="7"/>
@@ -8135,34 +8126,34 @@
     </row>
     <row r="126" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A126" s="5" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="B126" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="C126" s="7" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="D126" s="7"/>
       <c r="E126" s="7"/>
       <c r="F126" s="7"/>
       <c r="G126" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="H126" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="I126" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="J126" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="K126" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="L126" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="M126" s="7"/>
       <c r="N126" s="7"/>
@@ -8172,34 +8163,34 @@
     </row>
     <row r="127" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A127" s="5" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="B127" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="C127" s="7" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="D127" s="7"/>
       <c r="E127" s="7"/>
       <c r="F127" s="7"/>
       <c r="G127" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="H127" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="I127" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="J127" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="K127" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="L127" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="M127" s="7"/>
       <c r="N127" s="7"/>
@@ -8209,34 +8200,34 @@
     </row>
     <row r="128" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A128" s="5" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="B128" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="C128" s="7" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="D128" s="7"/>
       <c r="E128" s="7"/>
       <c r="F128" s="7"/>
       <c r="G128" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="H128" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="I128" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="J128" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="K128" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="L128" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="M128" s="7"/>
       <c r="N128" s="7"/>
@@ -8246,517 +8237,517 @@
     </row>
     <row r="129" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A129" s="5" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="B129" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="C129" s="7" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="D129" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="E129" t="s">
+        <v>625</v>
+      </c>
+      <c r="G129" s="7" t="s">
+        <v>624</v>
+      </c>
+      <c r="J129" s="7" t="s">
+        <v>624</v>
+      </c>
+      <c r="L129" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="M129" t="s">
+        <v>665</v>
+      </c>
+      <c r="N129" t="s">
+        <v>634</v>
+      </c>
+      <c r="O129" t="s">
+        <v>665</v>
+      </c>
+      <c r="P129" t="s">
         <v>628</v>
       </c>
-      <c r="G129" s="7" t="s">
-        <v>627</v>
-      </c>
-      <c r="J129" s="7" t="s">
-        <v>627</v>
-      </c>
-      <c r="L129" s="7" t="s">
-        <v>341</v>
-      </c>
-      <c r="M129" t="s">
-        <v>668</v>
-      </c>
-      <c r="N129" t="s">
-        <v>637</v>
-      </c>
-      <c r="O129" t="s">
-        <v>668</v>
-      </c>
-      <c r="P129" t="s">
-        <v>631</v>
-      </c>
       <c r="Q129" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
     </row>
     <row r="130" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A130" s="5" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="B130" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="C130" s="7" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="D130" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="E130" t="s">
+        <v>625</v>
+      </c>
+      <c r="G130" s="7" t="s">
+        <v>624</v>
+      </c>
+      <c r="J130" s="7" t="s">
+        <v>624</v>
+      </c>
+      <c r="L130" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="M130" t="s">
+        <v>665</v>
+      </c>
+      <c r="N130" t="s">
+        <v>634</v>
+      </c>
+      <c r="O130" t="s">
+        <v>665</v>
+      </c>
+      <c r="P130" t="s">
         <v>628</v>
       </c>
-      <c r="G130" s="7" t="s">
-        <v>627</v>
-      </c>
-      <c r="J130" s="7" t="s">
-        <v>627</v>
-      </c>
-      <c r="L130" s="7" t="s">
-        <v>341</v>
-      </c>
-      <c r="M130" t="s">
-        <v>668</v>
-      </c>
-      <c r="N130" t="s">
-        <v>637</v>
-      </c>
-      <c r="O130" t="s">
-        <v>668</v>
-      </c>
-      <c r="P130" t="s">
-        <v>631</v>
-      </c>
       <c r="Q130" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
     </row>
     <row r="131" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A131" s="5" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="B131" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="C131" s="7" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="D131" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="E131" t="s">
+        <v>625</v>
+      </c>
+      <c r="G131" s="7" t="s">
+        <v>624</v>
+      </c>
+      <c r="J131" s="7" t="s">
+        <v>624</v>
+      </c>
+      <c r="L131" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="M131" t="s">
+        <v>665</v>
+      </c>
+      <c r="N131" t="s">
+        <v>634</v>
+      </c>
+      <c r="O131" t="s">
+        <v>665</v>
+      </c>
+      <c r="P131" t="s">
         <v>628</v>
       </c>
-      <c r="G131" s="7" t="s">
-        <v>627</v>
-      </c>
-      <c r="J131" s="7" t="s">
-        <v>627</v>
-      </c>
-      <c r="L131" s="7" t="s">
-        <v>341</v>
-      </c>
-      <c r="M131" t="s">
-        <v>668</v>
-      </c>
-      <c r="N131" t="s">
-        <v>637</v>
-      </c>
-      <c r="O131" t="s">
-        <v>668</v>
-      </c>
-      <c r="P131" t="s">
-        <v>631</v>
-      </c>
       <c r="Q131" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
     </row>
     <row r="132" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A132" s="5" t="s">
+        <v>503</v>
+      </c>
+      <c r="B132" t="s">
         <v>506</v>
       </c>
-      <c r="B132" t="s">
-        <v>509</v>
-      </c>
       <c r="C132" s="7" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="D132" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="E132" t="s">
+        <v>625</v>
+      </c>
+      <c r="G132" s="7" t="s">
+        <v>624</v>
+      </c>
+      <c r="J132" s="7" t="s">
+        <v>624</v>
+      </c>
+      <c r="L132" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="M132" t="s">
+        <v>665</v>
+      </c>
+      <c r="N132" t="s">
+        <v>634</v>
+      </c>
+      <c r="O132" t="s">
+        <v>665</v>
+      </c>
+      <c r="P132" t="s">
         <v>628</v>
       </c>
-      <c r="G132" s="7" t="s">
-        <v>627</v>
-      </c>
-      <c r="J132" s="7" t="s">
-        <v>627</v>
-      </c>
-      <c r="L132" s="7" t="s">
-        <v>341</v>
-      </c>
-      <c r="M132" t="s">
-        <v>668</v>
-      </c>
-      <c r="N132" t="s">
-        <v>637</v>
-      </c>
-      <c r="O132" t="s">
-        <v>668</v>
-      </c>
-      <c r="P132" t="s">
-        <v>631</v>
-      </c>
       <c r="Q132" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
     </row>
     <row r="133" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A133" s="5" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="B133" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="C133" s="7" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="D133" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="E133" t="s">
+        <v>625</v>
+      </c>
+      <c r="G133" s="7" t="s">
+        <v>624</v>
+      </c>
+      <c r="J133" s="7" t="s">
+        <v>624</v>
+      </c>
+      <c r="L133" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="M133" t="s">
+        <v>665</v>
+      </c>
+      <c r="N133" t="s">
+        <v>634</v>
+      </c>
+      <c r="O133" t="s">
+        <v>665</v>
+      </c>
+      <c r="P133" t="s">
         <v>628</v>
       </c>
-      <c r="G133" s="7" t="s">
-        <v>627</v>
-      </c>
-      <c r="J133" s="7" t="s">
-        <v>627</v>
-      </c>
-      <c r="L133" s="7" t="s">
-        <v>341</v>
-      </c>
-      <c r="M133" t="s">
-        <v>668</v>
-      </c>
-      <c r="N133" t="s">
-        <v>637</v>
-      </c>
-      <c r="O133" t="s">
-        <v>668</v>
-      </c>
-      <c r="P133" t="s">
-        <v>631</v>
-      </c>
       <c r="Q133" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
     </row>
     <row r="134" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A134" s="5" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="B134" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="C134" s="7" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="D134" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="E134" t="s">
+        <v>625</v>
+      </c>
+      <c r="G134" s="7" t="s">
+        <v>624</v>
+      </c>
+      <c r="J134" s="7" t="s">
+        <v>624</v>
+      </c>
+      <c r="L134" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="M134" t="s">
+        <v>633</v>
+      </c>
+      <c r="N134" t="s">
+        <v>634</v>
+      </c>
+      <c r="O134" t="s">
+        <v>625</v>
+      </c>
+      <c r="P134" t="s">
         <v>628</v>
       </c>
-      <c r="G134" s="7" t="s">
-        <v>627</v>
-      </c>
-      <c r="J134" s="7" t="s">
-        <v>627</v>
-      </c>
-      <c r="L134" s="7" t="s">
-        <v>341</v>
-      </c>
-      <c r="M134" t="s">
-        <v>636</v>
-      </c>
-      <c r="N134" t="s">
-        <v>637</v>
-      </c>
-      <c r="O134" t="s">
-        <v>628</v>
-      </c>
-      <c r="P134" t="s">
-        <v>631</v>
-      </c>
       <c r="Q134" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
     </row>
     <row r="135" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A135" s="5" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="B135" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="C135" s="7" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="D135" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="E135" t="s">
+        <v>625</v>
+      </c>
+      <c r="G135" s="7" t="s">
+        <v>624</v>
+      </c>
+      <c r="J135" s="7" t="s">
+        <v>624</v>
+      </c>
+      <c r="L135" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="M135" t="s">
+        <v>666</v>
+      </c>
+      <c r="N135" t="s">
+        <v>634</v>
+      </c>
+      <c r="O135" t="s">
+        <v>625</v>
+      </c>
+      <c r="P135" t="s">
         <v>628</v>
       </c>
-      <c r="G135" s="7" t="s">
-        <v>627</v>
-      </c>
-      <c r="J135" s="7" t="s">
-        <v>627</v>
-      </c>
-      <c r="L135" s="7" t="s">
-        <v>341</v>
-      </c>
-      <c r="M135" t="s">
-        <v>669</v>
-      </c>
-      <c r="N135" t="s">
-        <v>637</v>
-      </c>
-      <c r="O135" t="s">
-        <v>628</v>
-      </c>
-      <c r="P135" t="s">
-        <v>631</v>
-      </c>
       <c r="Q135" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
     </row>
     <row r="136" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A136" s="5" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="B136" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="C136" s="7" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="D136" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="E136" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="G136" s="7" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="L136" s="7" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="M136" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="N136" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="O136" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="P136" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="Q136" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
     </row>
     <row r="137" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A137" s="5" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="B137" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="C137" s="7" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="D137" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="E137" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="G137" s="7" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="L137" s="7" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="M137" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="N137" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="O137" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="P137" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="Q137" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
     </row>
     <row r="138" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A138" s="5" t="s">
+        <v>523</v>
+      </c>
+      <c r="B138" t="s">
+        <v>524</v>
+      </c>
+      <c r="C138" s="7" t="s">
+        <v>525</v>
+      </c>
+      <c r="D138" t="s">
+        <v>639</v>
+      </c>
+      <c r="E138" t="s">
+        <v>625</v>
+      </c>
+      <c r="G138" s="7" t="s">
         <v>526</v>
       </c>
-      <c r="B138" t="s">
-        <v>527</v>
-      </c>
-      <c r="C138" s="7" t="s">
-        <v>528</v>
-      </c>
-      <c r="D138" t="s">
-        <v>642</v>
-      </c>
-      <c r="E138" t="s">
-        <v>628</v>
-      </c>
-      <c r="G138" s="7" t="s">
-        <v>529</v>
-      </c>
       <c r="L138" s="7" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="M138" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="N138" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="O138" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="P138" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="Q138" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
     </row>
     <row r="139" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A139" s="5" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="B139" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="C139" s="7" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="D139" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="E139" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="G139" s="7" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="L139" s="7" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="M139" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="N139" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="O139" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="P139" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="Q139" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
     </row>
     <row r="140" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A140" s="5" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="B140" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="C140" s="7" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="D140" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="E140" t="s">
+        <v>625</v>
+      </c>
+      <c r="G140" s="7" t="s">
+        <v>540</v>
+      </c>
+      <c r="L140" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="M140" t="s">
+        <v>625</v>
+      </c>
+      <c r="N140" t="s">
+        <v>625</v>
+      </c>
+      <c r="O140" t="s">
+        <v>627</v>
+      </c>
+      <c r="P140" t="s">
         <v>628</v>
       </c>
-      <c r="G140" s="7" t="s">
-        <v>543</v>
-      </c>
-      <c r="L140" s="7" t="s">
-        <v>341</v>
-      </c>
-      <c r="M140" t="s">
-        <v>628</v>
-      </c>
-      <c r="N140" t="s">
-        <v>628</v>
-      </c>
-      <c r="O140" t="s">
-        <v>630</v>
-      </c>
-      <c r="P140" t="s">
-        <v>631</v>
-      </c>
       <c r="Q140" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
     </row>
     <row r="141" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A141" s="5" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="B141" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="C141" s="7" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="D141" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="E141" t="s">
+        <v>625</v>
+      </c>
+      <c r="G141" s="7" t="s">
+        <v>540</v>
+      </c>
+      <c r="L141" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="M141" t="s">
+        <v>625</v>
+      </c>
+      <c r="N141" t="s">
+        <v>625</v>
+      </c>
+      <c r="O141" t="s">
+        <v>627</v>
+      </c>
+      <c r="P141" t="s">
         <v>628</v>
       </c>
-      <c r="G141" s="7" t="s">
-        <v>543</v>
-      </c>
-      <c r="L141" s="7" t="s">
-        <v>341</v>
-      </c>
-      <c r="M141" t="s">
-        <v>628</v>
-      </c>
-      <c r="N141" t="s">
-        <v>628</v>
-      </c>
-      <c r="O141" t="s">
-        <v>630</v>
-      </c>
-      <c r="P141" t="s">
-        <v>631</v>
-      </c>
       <c r="Q141" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
     </row>
   </sheetData>

--- a/inst/extdata/codelist.xlsx
+++ b/inst/extdata/codelist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\annesore\github\MoCiS2\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{524D8DB3-AF48-4CA1-B9C2-E8D3572652F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8329D15B-2FC4-483C-8994-189B0AEA2B1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2250" yWindow="450" windowWidth="19950" windowHeight="20115" tabRatio="877" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1755" uniqueCount="729">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1759" uniqueCount="732">
   <si>
     <t>PERC</t>
   </si>
@@ -2223,6 +2223,15 @@
   </si>
   <si>
     <t>CH07/895</t>
+  </si>
+  <si>
+    <t>BYXE</t>
+  </si>
+  <si>
+    <t>00103946</t>
+  </si>
+  <si>
+    <t>Byxelkrok</t>
   </si>
 </sst>
 </file>
@@ -2717,7 +2726,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D95"/>
+  <dimension ref="A1:D96"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="25.140625" style="16" customWidth="1"/>
@@ -2950,44 +2959,44 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>112</v>
+        <v>729</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>113</v>
+        <v>730</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>114</v>
+        <v>731</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>114</v>
+        <v>731</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -3001,7 +3010,7 @@
         <v>120</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>482</v>
+        <v>120</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -3014,246 +3023,246 @@
       <c r="C21" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="D21" t="s">
-        <v>620</v>
+      <c r="D21" s="7" t="s">
+        <v>482</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>123</v>
+        <v>120</v>
+      </c>
+      <c r="D22" t="s">
+        <v>620</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>478</v>
+        <v>144</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>150</v>
+        <v>478</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>314</v>
+        <v>148</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>110</v>
+        <v>149</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>111</v>
+        <v>150</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>479</v>
+        <v>150</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>151</v>
+        <v>314</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>152</v>
+        <v>110</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>153</v>
+        <v>111</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>153</v>
+        <v>479</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>125</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>126</v>
+        <v>152</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>154</v>
+        <v>124</v>
       </c>
       <c r="B35" s="16" t="s">
-        <v>155</v>
+        <v>125</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>156</v>
+        <v>126</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>156</v>
+        <v>126</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>315</v>
+        <v>154</v>
       </c>
       <c r="B36" s="16" t="s">
-        <v>146</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>480</v>
+        <v>155</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>154</v>
+        <v>315</v>
       </c>
       <c r="B37" s="16" t="s">
-        <v>155</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>156</v>
+        <v>146</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>480</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -3266,22 +3275,22 @@
       <c r="C39" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="D39" t="s">
-        <v>619</v>
+      <c r="D39" s="1" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="B40" s="16" t="s">
-        <v>158</v>
-      </c>
-      <c r="C40" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="D40" s="7" t="s">
-        <v>159</v>
+        <v>164</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D40" t="s">
+        <v>619</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -3295,329 +3304,329 @@
         <v>159</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>481</v>
+        <v>159</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>112</v>
+        <v>157</v>
       </c>
       <c r="B42" s="16" t="s">
-        <v>113</v>
+        <v>158</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>114</v>
+        <v>159</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>114</v>
+        <v>481</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>160</v>
+        <v>112</v>
       </c>
       <c r="B43" s="16" t="s">
-        <v>161</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>162</v>
+        <v>113</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B44" s="16" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="B45" s="16" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="B46" s="18" t="s">
-        <v>353</v>
+        <v>154</v>
+      </c>
+      <c r="B46" s="16" t="s">
+        <v>155</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B47" s="18" t="s">
+        <v>353</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="B47" s="16" t="s">
+      <c r="B48" s="16" t="s">
         <v>169</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="C48" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="D47" s="1" t="s">
+      <c r="D48" s="1" t="s">
         <v>170</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="9" t="s">
-        <v>354</v>
-      </c>
-      <c r="B48" s="10" t="s">
-        <v>356</v>
-      </c>
-      <c r="C48" s="9" t="s">
-        <v>355</v>
-      </c>
-      <c r="D48" s="9" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="9" t="s">
-        <v>451</v>
+        <v>354</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="9" t="s">
-        <v>361</v>
+        <v>451</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="9" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="9" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="9" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="9" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="9" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="9" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="9" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="9" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="9" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="9" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="9" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>396</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>395</v>
+        <v>393</v>
+      </c>
+      <c r="C61" s="9" t="s">
+        <v>392</v>
+      </c>
+      <c r="D61" s="9" t="s">
+        <v>392</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="9" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>399</v>
-      </c>
-      <c r="C62" s="9" t="s">
-        <v>398</v>
-      </c>
-      <c r="D62" s="9" t="s">
-        <v>398</v>
+        <v>396</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>395</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="9" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="9" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="D64" s="9" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -3631,426 +3640,440 @@
         <v>404</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>517</v>
+        <v>404</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="9" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C66" s="9" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>407</v>
+        <v>517</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="9" t="s">
+        <v>406</v>
+      </c>
+      <c r="B67" s="10" t="s">
+        <v>408</v>
+      </c>
+      <c r="C67" s="9" t="s">
+        <v>407</v>
+      </c>
+      <c r="D67" s="9" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" s="9" t="s">
         <v>409</v>
       </c>
-      <c r="B67" s="10" t="s">
+      <c r="B68" s="10" t="s">
         <v>411</v>
       </c>
-      <c r="C67" s="9" t="s">
+      <c r="C68" s="9" t="s">
         <v>410</v>
       </c>
-      <c r="D67" s="9" t="s">
+      <c r="D68" s="9" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A68" s="11" t="s">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" s="11" t="s">
         <v>412</v>
       </c>
-      <c r="B68" s="10" t="s">
+      <c r="B69" s="10" t="s">
         <v>414</v>
       </c>
-      <c r="C68" s="11" t="s">
+      <c r="C69" s="11" t="s">
         <v>413</v>
       </c>
-      <c r="D68" s="11" t="s">
+      <c r="D69" s="11" t="s">
         <v>413</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A69" s="9" t="s">
-        <v>415</v>
-      </c>
-      <c r="B69" s="10" t="s">
-        <v>417</v>
-      </c>
-      <c r="C69" s="9" t="s">
-        <v>416</v>
-      </c>
-      <c r="D69" s="9" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="9" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="B70" s="10" t="s">
-        <v>420</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
+      </c>
+      <c r="C70" s="9" t="s">
+        <v>416</v>
+      </c>
+      <c r="D70" s="9" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="9" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="B71" s="10" t="s">
-        <v>423</v>
-      </c>
-      <c r="C71" s="9" t="s">
-        <v>422</v>
-      </c>
-      <c r="D71" s="9" t="s">
-        <v>422</v>
+        <v>420</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>419</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="B72" s="10" t="s">
+        <v>423</v>
+      </c>
+      <c r="C72" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="D72" s="9" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" s="9" t="s">
         <v>424</v>
       </c>
-      <c r="B72" s="10" t="s">
+      <c r="B73" s="10" t="s">
         <v>426</v>
       </c>
-      <c r="C72" s="9" t="s">
+      <c r="C73" s="9" t="s">
         <v>425</v>
       </c>
-      <c r="D72" s="9" t="s">
+      <c r="D73" s="9" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A73" s="11" t="s">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" s="11" t="s">
         <v>427</v>
       </c>
-      <c r="B73" s="10" t="s">
+      <c r="B74" s="10" t="s">
         <v>429</v>
       </c>
-      <c r="C73" s="11" t="s">
+      <c r="C74" s="11" t="s">
         <v>428</v>
       </c>
-      <c r="D73" s="11" t="s">
+      <c r="D74" s="11" t="s">
         <v>428</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A74" s="9" t="s">
-        <v>430</v>
-      </c>
-      <c r="B74" s="10" t="s">
-        <v>432</v>
-      </c>
-      <c r="C74" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="D74" s="9" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="9" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="B75" s="10" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="C75" s="9" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="D75" s="9" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="9" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="B76" s="10" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="C76" s="9" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D76" s="9" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="9" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="B77" s="10" t="s">
-        <v>441</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>440</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
+      </c>
+      <c r="C77" s="9" t="s">
+        <v>437</v>
+      </c>
+      <c r="D77" s="9" t="s">
+        <v>437</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="9" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="B78" s="10" t="s">
-        <v>444</v>
-      </c>
-      <c r="C78" s="9" t="s">
-        <v>443</v>
-      </c>
-      <c r="D78" s="9" t="s">
-        <v>443</v>
+        <v>441</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>440</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="9" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="B79" s="10" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="C79" s="9" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="D79" s="9" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="9" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="B80" s="10" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="C80" s="9" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="D80" s="9" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="9" t="s">
-        <v>655</v>
-      </c>
-      <c r="B81" s="16" t="s">
-        <v>654</v>
+        <v>448</v>
+      </c>
+      <c r="B81" s="10" t="s">
+        <v>450</v>
       </c>
       <c r="C81" s="9" t="s">
-        <v>653</v>
-      </c>
-      <c r="D81" t="s">
-        <v>653</v>
+        <v>449</v>
+      </c>
+      <c r="D81" s="9" t="s">
+        <v>449</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="9" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="B82" s="16" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="C82" s="9" t="s">
-        <v>656</v>
-      </c>
-      <c r="D82" s="9" t="s">
-        <v>656</v>
+        <v>653</v>
+      </c>
+      <c r="D82" t="s">
+        <v>653</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="9" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="B83" s="16" t="s">
-        <v>660</v>
-      </c>
-      <c r="C83" t="s">
-        <v>659</v>
-      </c>
-      <c r="D83" t="s">
-        <v>659</v>
+        <v>657</v>
+      </c>
+      <c r="C83" s="9" t="s">
+        <v>656</v>
+      </c>
+      <c r="D83" s="9" t="s">
+        <v>656</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="9" t="s">
+        <v>661</v>
+      </c>
+      <c r="B84" s="16" t="s">
+        <v>660</v>
+      </c>
+      <c r="C84" t="s">
+        <v>659</v>
+      </c>
+      <c r="D84" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85" s="9" t="s">
         <v>664</v>
       </c>
-      <c r="B84" s="16" t="s">
+      <c r="B85" s="16" t="s">
         <v>662</v>
       </c>
-      <c r="C84" s="9" t="s">
+      <c r="C85" s="9" t="s">
         <v>663</v>
       </c>
-      <c r="D84" s="9" t="s">
+      <c r="D85" s="9" t="s">
         <v>663</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A85" s="1" t="s">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="B85" s="16" t="s">
+      <c r="B86" s="16" t="s">
         <v>146</v>
       </c>
-      <c r="C85" s="7" t="s">
+      <c r="C86" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="D85" s="7" t="s">
+      <c r="D86" s="7" t="s">
         <v>147</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A86" s="21" t="s">
-        <v>677</v>
-      </c>
-      <c r="B86" s="16" t="s">
-        <v>687</v>
-      </c>
-      <c r="C86" t="s">
-        <v>667</v>
-      </c>
-      <c r="D86" t="s">
-        <v>667</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="21" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B87" s="16" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="C87" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="D87" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" s="21" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B88" s="16" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="C88" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D88" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="21" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B89" s="16" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="C89" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="D89" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="21" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B90" s="16" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="C90" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="D90" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="21" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B91" s="16" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="C91" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="D91" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="21" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B92" s="16" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="C92" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="D92" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" s="21" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B93" s="16" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C93" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="D93" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="21" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B94" s="16" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="C94" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="D94" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="21" t="s">
+        <v>685</v>
+      </c>
+      <c r="B95" s="16" t="s">
+        <v>695</v>
+      </c>
+      <c r="C95" t="s">
+        <v>675</v>
+      </c>
+      <c r="D95" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A96" s="21" t="s">
         <v>686</v>
       </c>
-      <c r="B95" s="16" t="s">
+      <c r="B96" s="16" t="s">
         <v>696</v>
       </c>
-      <c r="C95" t="s">
+      <c r="C96" t="s">
         <v>676</v>
       </c>
-      <c r="D95" t="s">
+      <c r="D96" t="s">
         <v>676</v>
       </c>
     </row>
